--- a/data/trans_dic/P79_n_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P79_n_R2-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,38; 9,56</t>
+          <t>5,52; 9,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,35; 8,08</t>
+          <t>5,64; 8,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,63; 8,22</t>
+          <t>6,13; 8,43</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,6</t>
+          <t>3,35; 5,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,39</t>
+          <t>3,15; 5,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,17</t>
+          <t>3,45; 4,76</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,4</t>
+          <t>0,51; 2,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,82</t>
+          <t>0,57; 2,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,75</t>
+          <t>0,77; 1,87</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 4,5</t>
+          <t>3,47; 4,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 4,28</t>
+          <t>3,42; 4,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 4,12</t>
+          <t>3,66; 4,63</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37430</t>
+          <t>42868</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50120</t>
+          <t>57516</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87550</t>
+          <t>100384</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27678; 49250</t>
+          <t>31952; 56036</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40414; 61035</t>
+          <t>46396; 68692</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71501; 104394</t>
+          <t>85834; 118086</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>81100</t>
+          <t>94442</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>73632</t>
+          <t>85108</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>154733</t>
+          <t>179550</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54510; 105271</t>
+          <t>74678; 119722</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52745; 98255</t>
+          <t>68393; 108642</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>118829; 188953</t>
+          <t>151894; 209709</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14157</t>
+          <t>17942</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3387; 15528</t>
+          <t>3619; 17358</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3179; 12007</t>
+          <t>4182; 14738</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8429; 22810</t>
+          <t>11135; 26978</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>126095</t>
+          <t>146683</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>130345</t>
+          <t>151194</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>256440</t>
+          <t>297877</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>98670; 155325</t>
+          <t>122096; 173986</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>105257; 156520</t>
+          <t>127512; 175763</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>217278; 292747</t>
+          <t>265589; 335344</t>
         </is>
       </c>
     </row>
